--- a/ig/DM-MAI-2026/ValueSet-JDV-J16-ActeSpecifique-ROR.xlsx
+++ b/ig/DM-MAI-2026/ValueSet-JDV-J16-ActeSpecifique-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2529" uniqueCount="2527">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2561" uniqueCount="2559">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260505120000</t>
+    <t>20260601120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-05T12:00:00+01:00</t>
+    <t>2026-06-01T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -7386,205 +7386,301 @@
     <t>1582</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en cardiologie</t>
+    <t>Prise en charge spécialisée et continue en cardiologie</t>
   </si>
   <si>
     <t>1583</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie cardiaque et gros vaisseaux</t>
+    <t>Prise en charge spécialisée et continue en chirurgie cardiaque et gros vaisseaux</t>
   </si>
   <si>
     <t>1584</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie digestive et viscérale</t>
+    <t>Prise en charge spécialisée et continue en chirurgie digestive et viscérale</t>
   </si>
   <si>
     <t>1585</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie maxillo-faciale et stomatologie</t>
+    <t>Prise en charge spécialisée et continue en chirurgie maxillo-faciale et stomatologie</t>
   </si>
   <si>
     <t>1586</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie orthopédique et traumatologie</t>
+    <t>Prise en charge spécialisée et continue en chirurgie orthopédique et traumatologie</t>
   </si>
   <si>
     <t>1587</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie pédiatrique orthopédique et traumatologie</t>
+    <t>Prise en charge spécialisée et continue en chirurgie pédiatrique orthopédique et traumatologie</t>
   </si>
   <si>
     <t>1588</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie pédiatrique viscérale et digestive</t>
+    <t>Prise en charge spécialisée et continue en chirurgie pédiatrique viscérale et digestive</t>
   </si>
   <si>
     <t>1589</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie thoracique et pulmonaire</t>
+    <t>Prise en charge spécialisée et continue en chirurgie thoracique et pulmonaire</t>
   </si>
   <si>
     <t>1590</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie vasculaire</t>
+    <t>Prise en charge spécialisée et continue en chirurgie vasculaire</t>
   </si>
   <si>
     <t>1591</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en dermatologie</t>
+    <t>Prise en charge spécialisée et continue en dermatologie</t>
   </si>
   <si>
     <t>1592</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en endocrinologie</t>
+    <t>Prise en charge spécialisée et continue en endocrinologie</t>
   </si>
   <si>
     <t>1593</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en gériatrie (gérontologie)</t>
+    <t>Prise en charge spécialisée et continue en gériatrie (gérontologie)</t>
   </si>
   <si>
     <t>1594</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en gynécologie</t>
+    <t>Prise en charge spécialisée et continue en gynécologie</t>
   </si>
   <si>
     <t>1595</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en hématologie</t>
+    <t>Prise en charge spécialisée et continue en hématologie</t>
   </si>
   <si>
     <t>1596</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en hépato-gastro-entérologie</t>
+    <t>Prise en charge spécialisée et continue en hépato-gastro-entérologie</t>
   </si>
   <si>
     <t>1597</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en maladies infectieuses et tropicales</t>
+    <t>Prise en charge spécialisée et continue en maladies infectieuses et tropicales</t>
   </si>
   <si>
     <t>1598</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en médecine interne</t>
+    <t>Prise en charge spécialisée et continue en médecine interne</t>
   </si>
   <si>
     <t>1599</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en médecine vasculaire</t>
+    <t>Prise en charge spécialisée et continue en médecine vasculaire</t>
   </si>
   <si>
     <t>1600</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en néphrologie (dont dialyse)</t>
+    <t>Prise en charge spécialisée et continue en néphrologie (dont dialyse)</t>
   </si>
   <si>
     <t>1601</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en neurochirurgie</t>
+    <t>Prise en charge spécialisée et continue en neurochirurgie</t>
   </si>
   <si>
     <t>1602</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en neurologie</t>
+    <t>Prise en charge spécialisée et continue en neurologie</t>
   </si>
   <si>
     <t>1603</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en oncologie</t>
+    <t>Prise en charge spécialisée et continue en oncologie</t>
   </si>
   <si>
     <t>1604</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en ophtalmologie</t>
+    <t>Prise en charge spécialisée et continue en ophtalmologie</t>
   </si>
   <si>
     <t>1605</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en oto-rhino-laryngologie (ORL) et chirurgie cervico-faciale</t>
+    <t>Prise en charge spécialisée et continue en oto-rhino-laryngologie (ORL) et chirurgie cervico-faciale</t>
   </si>
   <si>
     <t>1606</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en pédiatrie</t>
+    <t>Prise en charge spécialisée et continue en pédiatrie</t>
   </si>
   <si>
     <t>1607</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en pneumologie</t>
+    <t>Prise en charge spécialisée et continue en pneumologie</t>
   </si>
   <si>
     <t>1608</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en rhumatologie</t>
+    <t>Prise en charge spécialisée et continue en rhumatologie</t>
   </si>
   <si>
     <t>1609</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en urologie</t>
+    <t>Prise en charge spécialisée et continue en urologie</t>
   </si>
   <si>
     <t>1610</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en caisson oxygène hyperbare</t>
+    <t>Prise en charge spécialisée et continue en caisson oxygène hyperbare</t>
   </si>
   <si>
     <t>1611</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie de la main SOS main</t>
+    <t>Prise en charge spécialisée et continue en chirurgie de la main SOS main</t>
   </si>
   <si>
     <t>1612</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en odontologie</t>
+    <t>Prise en charge spécialisée et continue en odontologie</t>
   </si>
   <si>
     <t>1613</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en psychiatrie (dont équipe de liaison)</t>
+    <t>Prise en charge spécialisée et continue en psychiatrie (dont équipe de liaison)</t>
   </si>
   <si>
     <t>1614</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en radiologie interventionnelle</t>
+    <t>Prise en charge spécialisée et continue en radiologie interventionnelle</t>
   </si>
   <si>
     <t>1615</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) rachis</t>
+    <t>Prise en charge spécialisée et continue rachis</t>
+  </si>
+  <si>
+    <t>1616</t>
+  </si>
+  <si>
+    <t>Pédicurie-podologie conventionnée du pied diabétique de grade 2 et 3</t>
+  </si>
+  <si>
+    <t>1617</t>
+  </si>
+  <si>
+    <t>Pédicurie-podologie conventionnée soins de support oncologie</t>
+  </si>
+  <si>
+    <t>1618</t>
+  </si>
+  <si>
+    <t>Orthoplastie (appareillage d’orteil)</t>
+  </si>
+  <si>
+    <t>1619</t>
+  </si>
+  <si>
+    <t>Orthonyxie (appareillage d’ongle)</t>
+  </si>
+  <si>
+    <t>1620</t>
+  </si>
+  <si>
+    <t>Onychoplastie (reconstruction de l’ongle)</t>
+  </si>
+  <si>
+    <t>1621</t>
+  </si>
+  <si>
+    <t>Orthèse plantaire (semelle orthopédique)</t>
+  </si>
+  <si>
+    <t>1622</t>
+  </si>
+  <si>
+    <t>Bilan diagnostique podologique de la prévention de la chute</t>
+  </si>
+  <si>
+    <t>1623</t>
+  </si>
+  <si>
+    <t>Rééducation du pied (sous la cheville)</t>
+  </si>
+  <si>
+    <t>1624</t>
+  </si>
+  <si>
+    <t>Contention nocturne</t>
+  </si>
+  <si>
+    <t>1625</t>
+  </si>
+  <si>
+    <t>Soin de pédicurie</t>
+  </si>
+  <si>
+    <t>1626</t>
+  </si>
+  <si>
+    <t>Traitement de la verrue plantaire par azote liquide</t>
+  </si>
+  <si>
+    <t>1627</t>
+  </si>
+  <si>
+    <t>Traitement sans douleur de l’ongle incarné par phénolisation (protocole de coopération)</t>
+  </si>
+  <si>
+    <t>1628</t>
+  </si>
+  <si>
+    <t>Prélèvement unguéal pour analyse biologique (protocole de coopération)</t>
+  </si>
+  <si>
+    <t>1629</t>
+  </si>
+  <si>
+    <t>Confection de semelle de comblement en polyuréthane (PU) pour amputation partielle du pied</t>
+  </si>
+  <si>
+    <t>1630</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et continue en pédopsychiatrie (dont équipe de liaison)</t>
+  </si>
+  <si>
+    <t>1631</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et continue SOS main</t>
   </si>
   <si>
     <t/>
@@ -7855,7 +7951,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B1251"/>
+  <dimension ref="A1:B1267"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -17859,15 +17955,143 @@
         <v>2524</v>
       </c>
       <c r="B1250" t="s" s="2">
-        <v>2524</v>
+        <v>2525</v>
       </c>
     </row>
     <row r="1251">
       <c r="A1251" t="s" s="2">
-        <v>2525</v>
+        <v>2526</v>
       </c>
       <c r="B1251" t="s" s="2">
-        <v>2526</v>
+        <v>2527</v>
+      </c>
+    </row>
+    <row r="1252">
+      <c r="A1252" t="s" s="2">
+        <v>2528</v>
+      </c>
+      <c r="B1252" t="s" s="2">
+        <v>2529</v>
+      </c>
+    </row>
+    <row r="1253">
+      <c r="A1253" t="s" s="2">
+        <v>2530</v>
+      </c>
+      <c r="B1253" t="s" s="2">
+        <v>2531</v>
+      </c>
+    </row>
+    <row r="1254">
+      <c r="A1254" t="s" s="2">
+        <v>2532</v>
+      </c>
+      <c r="B1254" t="s" s="2">
+        <v>2533</v>
+      </c>
+    </row>
+    <row r="1255">
+      <c r="A1255" t="s" s="2">
+        <v>2534</v>
+      </c>
+      <c r="B1255" t="s" s="2">
+        <v>2535</v>
+      </c>
+    </row>
+    <row r="1256">
+      <c r="A1256" t="s" s="2">
+        <v>2536</v>
+      </c>
+      <c r="B1256" t="s" s="2">
+        <v>2537</v>
+      </c>
+    </row>
+    <row r="1257">
+      <c r="A1257" t="s" s="2">
+        <v>2538</v>
+      </c>
+      <c r="B1257" t="s" s="2">
+        <v>2539</v>
+      </c>
+    </row>
+    <row r="1258">
+      <c r="A1258" t="s" s="2">
+        <v>2540</v>
+      </c>
+      <c r="B1258" t="s" s="2">
+        <v>2541</v>
+      </c>
+    </row>
+    <row r="1259">
+      <c r="A1259" t="s" s="2">
+        <v>2542</v>
+      </c>
+      <c r="B1259" t="s" s="2">
+        <v>2543</v>
+      </c>
+    </row>
+    <row r="1260">
+      <c r="A1260" t="s" s="2">
+        <v>2544</v>
+      </c>
+      <c r="B1260" t="s" s="2">
+        <v>2545</v>
+      </c>
+    </row>
+    <row r="1261">
+      <c r="A1261" t="s" s="2">
+        <v>2546</v>
+      </c>
+      <c r="B1261" t="s" s="2">
+        <v>2547</v>
+      </c>
+    </row>
+    <row r="1262">
+      <c r="A1262" t="s" s="2">
+        <v>2548</v>
+      </c>
+      <c r="B1262" t="s" s="2">
+        <v>2549</v>
+      </c>
+    </row>
+    <row r="1263">
+      <c r="A1263" t="s" s="2">
+        <v>2550</v>
+      </c>
+      <c r="B1263" t="s" s="2">
+        <v>2551</v>
+      </c>
+    </row>
+    <row r="1264">
+      <c r="A1264" t="s" s="2">
+        <v>2552</v>
+      </c>
+      <c r="B1264" t="s" s="2">
+        <v>2553</v>
+      </c>
+    </row>
+    <row r="1265">
+      <c r="A1265" t="s" s="2">
+        <v>2554</v>
+      </c>
+      <c r="B1265" t="s" s="2">
+        <v>2555</v>
+      </c>
+    </row>
+    <row r="1266">
+      <c r="A1266" t="s" s="2">
+        <v>2556</v>
+      </c>
+      <c r="B1266" t="s" s="2">
+        <v>2556</v>
+      </c>
+    </row>
+    <row r="1267">
+      <c r="A1267" t="s" s="2">
+        <v>2557</v>
+      </c>
+      <c r="B1267" t="s" s="2">
+        <v>2558</v>
       </c>
     </row>
   </sheetData>
